--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
